--- a/data/processed_data/gbif_map.xlsx
+++ b/data/processed_data/gbif_map.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1744,21 +1744,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OCHLEROTATUS SCAPULARIS</t>
+          <t>ANOPHELES SSP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ochlerotatus scapularis (Rondani, 1848)</t>
+          <t>Anopheles Meigen, 1818</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SYNONYM</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="D29">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1782,24 +1782,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aedes</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Aedes scapularis</t>
+          <t>Anopheles</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ANOPHELES SSP</t>
+          <t>LUTZOMYIA LONGIPALPIS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Anopheles Meigen, 1818</t>
+          <t>Lutzomyia longipalpis (Lutz &amp; Neiva, 1912)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1808,7 +1803,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1827,24 +1822,29 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Culicidae</t>
+          <t>Psychodidae</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Anopheles</t>
+          <t>Lutzomyia</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Lutzomyia longipalpis</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LUTZOMYIA LONGIPALPIS</t>
+          <t>NYSSOMYIA NEIVAI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lutzomyia longipalpis (Lutz &amp; Neiva, 1912)</t>
+          <t>Nyssomyia neivai (Pinto, 1926)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1877,33 +1877,33 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Lutzomyia</t>
+          <t>Nyssomyia</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Lutzomyia longipalpis</t>
+          <t>Nyssomyia neivai</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NYSSOMYIA NEIVAI</t>
+          <t>LUTZOMYIA SHANNONI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nyssomyia neivai (Pinto, 1926)</t>
+          <t>Lutzomyia shannoni (Dyar, 1929)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>SYNONYM</t>
         </is>
       </c>
       <c r="D32">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1927,33 +1927,33 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Nyssomyia</t>
+          <t>Psathyromyia</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nyssomyia neivai</t>
+          <t>Psathyromyia shannoni</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LUTZOMYIA SHANNONI</t>
+          <t>BRUMPTOMYIA BRUMPTI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lutzomyia shannoni (Dyar, 1929)</t>
+          <t>Brumptomyia brumpti Larroussee</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SYNONYM</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="D33">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1977,24 +1977,24 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Psathyromyia</t>
+          <t>Brumptomyia</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Psathyromyia shannoni</t>
+          <t>Brumptomyia brumpti</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BRUMPTOMYIA BRUMPTI</t>
+          <t>MIGONEMYIA MIGONEI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Brumptomyia brumpti Larroussee</t>
+          <t>Migonemyia migonei França, 1920</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2027,24 +2027,24 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Brumptomyia</t>
+          <t>Migonemyia</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Brumptomyia brumpti</t>
+          <t>Migonemyia migonei</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MIGONEMYIA MIGONEI</t>
+          <t>NYSSOMYIA WHITMANI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Migonemyia migonei França, 1920</t>
+          <t>Nyssomyia whitmani (Antunes &amp; Coutinho, 1939)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2077,24 +2077,24 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Migonemyia</t>
+          <t>Nyssomyia</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Migonemyia migonei</t>
+          <t>Nyssomyia whitmani</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NYSSOMYIA WHITMANI</t>
+          <t>BRUMPTOMYIA AVELLARI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nyssomyia whitmani (Antunes &amp; Coutinho, 1939)</t>
+          <t>Brumptomyia avellari (Lima, 1932)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2127,24 +2127,24 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Nyssomyia</t>
+          <t>Brumptomyia</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Nyssomyia whitmani</t>
+          <t>Brumptomyia avellari</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BRUMPTOMYIA AVELLARI</t>
+          <t>LUTZOMYIA WHITMANI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Brumptomyia avellari (Lima, 1932)</t>
+          <t>Lutzomyia França, 1924</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="D37">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2177,24 +2177,19 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Brumptomyia</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Brumptomyia avellari</t>
+          <t>Lutzomyia</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LUTZOMYIA WHITMANI</t>
+          <t>EVANDROMYIA EVANDROI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lutzomyia França, 1924</t>
+          <t>Evandromyia evandroi (Lima &amp; Antunes, 1936)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2203,7 +2198,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2227,19 +2222,24 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Lutzomyia</t>
+          <t>Evandromyia</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Evandromyia evandroi</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EVANDROMYIA EVANDROI</t>
+          <t>BRUMPTOMYIA GUIMARAESI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Evandromyia evandroi (Lima &amp; Antunes, 1936)</t>
+          <t>Brumptomyia guimaraesi (Coutinho &amp; Barretto, 1941)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2272,24 +2272,24 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
+          <t>Brumptomyia</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Evandromyia evandroi</t>
+          <t>Brumptomyia guimaraesi</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BRUMPTOMYIA GUIMARAESI</t>
+          <t>LUTZOMYIA NEIVAI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Brumptomyia guimaraesi (Coutinho &amp; Barretto, 1941)</t>
+          <t>Lutzomyia França, 1924</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2322,24 +2322,19 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Brumptomyia</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Brumptomyia guimaraesi</t>
+          <t>Lutzomyia</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LUTZOMYIA NEIVAI</t>
+          <t>EVANDROMYIA CORTELEZZI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lutzomyia França, 1924</t>
+          <t>Evandromyia cortelezzii (Brèthes, 1923)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2348,7 +2343,7 @@
         </is>
       </c>
       <c r="D41">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2372,19 +2367,24 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Lutzomyia</t>
+          <t>Evandromyia</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Evandromyia cortelezzii</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EVANDROMYIA CORTELEZZI</t>
+          <t>LUTZOMYIA PESSOAI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Evandromyia cortelezzii (Brèthes, 1923)</t>
+          <t>Lutzomyia pescei (Hertig, 1943)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="D42">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2417,24 +2417,24 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
+          <t>Lutzomyia</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Evandromyia cortelezzii</t>
+          <t>Lutzomyia pescei</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LUTZOMYIA PESSOAI</t>
+          <t>BRUMPTOMYIA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lutzomyia pescei (Hertig, 1943)</t>
+          <t>Brumptomyia França &amp; Parrot, 1921</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="D43">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2467,24 +2467,19 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Lutzomyia</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Lutzomyia pescei</t>
+          <t>Brumptomyia</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BRUMPTOMYIA</t>
+          <t>LUTZOMYIA LENTI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brumptomyia França &amp; Parrot, 1921</t>
+          <t>Lutzomyia França, 1924</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2493,7 +2488,7 @@
         </is>
       </c>
       <c r="D44">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2517,19 +2512,19 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Brumptomyia</t>
+          <t>Lutzomyia</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LUTZOMYIA LENTI</t>
+          <t>PSATHYROMYIA SHANNONI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lutzomyia França, 1924</t>
+          <t>Psathyromyia shannoni (Dyar, 1929)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2538,7 +2533,7 @@
         </is>
       </c>
       <c r="D45">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2562,19 +2557,24 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Lutzomyia</t>
+          <t>Psathyromyia</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Psathyromyia shannoni</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PSATHYROMYIA SHANNONI</t>
+          <t>PINTOMYIA PESSOAI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Psathyromyia shannoni (Dyar, 1929)</t>
+          <t>Pintomyia pessoai (Coutinho &amp; Barretto, 1940)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2607,24 +2607,24 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Psathyromyia</t>
+          <t>Pintomyia</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Psathyromyia shannoni</t>
+          <t>Pintomyia pessoai</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PINTOMYIA PESSOAI</t>
+          <t>EVANDROMYIA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pintomyia pessoai (Coutinho &amp; Barretto, 1940)</t>
+          <t>Evandromyia Mangabeira, 1941</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D47">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2657,24 +2657,19 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Pintomyia</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Pintomyia pessoai</t>
+          <t>Evandromyia</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EVANDROMYIA</t>
+          <t>PINTOMYIA KUSCHELI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Evandromyia Mangabeira, 1941</t>
+          <t>Pintomyia kuscheli (Le Pont, Martínez &amp; Torrez-Espejo, 1998)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2683,7 +2678,7 @@
         </is>
       </c>
       <c r="D48">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2707,19 +2702,24 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
+          <t>Pintomyia</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Pintomyia kuscheli</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PINTOMYIA KUSCHELI</t>
+          <t>EVANDROMYIA CARMELINOI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pintomyia kuscheli (Le Pont, Martínez &amp; Torrez-Espejo, 1998)</t>
+          <t>Evandromyia carmelinoi (Ryan, Fraiha, Lainson &amp; Shaw, 1986)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2752,24 +2752,24 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Pintomyia</t>
+          <t>Evandromyia</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Pintomyia kuscheli</t>
+          <t>Evandromyia carmelinoi</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EVANDROMYIA CARMELINOI</t>
+          <t>LUTZOMYIA INTERMEDIA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Evandromyia carmelinoi (Ryan, Fraiha, Lainson &amp; Shaw, 1986)</t>
+          <t>Lutzomyia França, 1924</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="D50">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2802,24 +2802,19 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Evandromyia carmelinoi</t>
+          <t>Lutzomyia</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LUTZOMYIA INTERMEDIA</t>
+          <t>EVANDROMYIA ALDEMYIA TERMITOPHILA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lutzomyia França, 1924</t>
+          <t>Evandromyia Mangabeira, 1941</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2828,7 +2823,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2852,19 +2847,19 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Lutzomyia</t>
+          <t>Evandromyia</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EVANDROMYIA ALDEMYIA TERMITOPHILA</t>
+          <t>LUTZOMYIA FISCHERI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Evandromyia Mangabeira, 1941</t>
+          <t>Lutzomyia França, 1924</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2873,7 +2868,7 @@
         </is>
       </c>
       <c r="D52">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2897,14 +2892,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
+          <t>Lutzomyia</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LUTZOMYIA FISCHERI</t>
+          <t>LUTZOMYIA QUINQUEFER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2949,7 +2944,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LUTZOMYIA QUINQUEFER</t>
+          <t>LUTZOMYIA MONTICOLA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2994,12 +2989,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LUTZOMYIA MONTICOLA</t>
+          <t>EVANDROMYIA LENTI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lutzomyia França, 1924</t>
+          <t>Evandromyia lenti (Mangabeira, 1938)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3008,7 +3003,7 @@
         </is>
       </c>
       <c r="D55">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3032,19 +3027,24 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Lutzomyia</t>
+          <t>Evandromyia</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Evandromyia lenti</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EVANDROMYIA LENTI</t>
+          <t>PINTOMYIA FISCHERI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Evandromyia lenti (Mangabeira, 1938)</t>
+          <t>Pintomyia fischeri (Pinto, 1926)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3077,24 +3077,24 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
+          <t>Pintomyia</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Evandromyia lenti</t>
+          <t>Pintomyia fischeri</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PINTOMYIA FISCHERI</t>
+          <t>MICROPYGOMYIA QUINQUEFER</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pintomyia fischeri (Pinto, 1926)</t>
+          <t>Micropygomyia quinquefer (Dyar, 1929)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3127,24 +3127,24 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Pintomyia</t>
+          <t>Micropygomyia</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Pintomyia fischeri</t>
+          <t>Micropygomyia quinquefer</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MICROPYGOMYIA QUINQUEFER</t>
+          <t>BRUMPTOMYIA CUNHAI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Micropygomyia quinquefer (Dyar, 1929)</t>
+          <t>Brumptomyia cunhai (Mangabeira, 1942)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3177,24 +3177,24 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Micropygomyia</t>
+          <t>Brumptomyia</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Micropygomyia quinquefer</t>
+          <t>Brumptomyia cunhai</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BRUMPTOMYIA CUNHAI</t>
+          <t>MYGONEMYIA MIGONEI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Brumptomyia cunhai (Mangabeira, 1942)</t>
+          <t>Migonemyia migonei França, 1920</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="D59">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3227,24 +3227,24 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Brumptomyia</t>
+          <t>Migonemyia</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Brumptomyia cunhai</t>
+          <t>Migonemyia migonei</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MYGONEMYIA MIGONEI</t>
+          <t>LUTZOMYIA CRUZI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Migonemyia migonei França, 1920</t>
+          <t>Lutzomyia cruzi (Mangabeira, 1938)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="D60">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3277,79 +3277,79 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Migonemyia</t>
+          <t>Lutzomyia</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Migonemyia migonei</t>
+          <t>Lutzomyia cruzi</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>LUTZOMYIA CRUZI</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Lutzomyia cruzi (Mangabeira, 1938)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
       <c r="D61">
-        <v>99</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Animalia</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Arthropoda</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Diptera</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PSATHYROMYIA PUNTIGENICULATA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Psathyromyia punctigeniculata (Floch &amp; Abonnenc, 1944)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>95</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Animalia</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Arthropoda</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Diptera</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
         <is>
           <t>Psychodidae</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Lutzomyia</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Lutzomyia cruzi</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="D62">
-        <v>100</v>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Psathyromyia</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Psathyromyia punctigeniculata</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PSATHYROMYIA PUNTIGENICULATA</t>
+          <t>PINTOMYIA MISIONENSIS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Psathyromyia punctigeniculata (Floch &amp; Abonnenc, 1944)</t>
+          <t>Pintomyia misionensis (Castro, 1959)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="D63">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3382,24 +3382,24 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Psathyromyia</t>
+          <t>Pintomyia</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Psathyromyia punctigeniculata</t>
+          <t>Pintomyia misionensis</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PINTOMYIA MISIONENSIS</t>
+          <t>NISSOMYIA NEIVAI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pintomyia misionensis (Castro, 1959)</t>
+          <t>Nyssomyia neivai (Pinto, 1926)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="D64">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3432,24 +3432,24 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Pintomyia</t>
+          <t>Nyssomyia</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Pintomyia misionensis</t>
+          <t>Nyssomyia neivai</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NISSOMYIA NEIVAI</t>
+          <t>BRUMPTOMYIA SPP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nyssomyia neivai (Pinto, 1926)</t>
+          <t>Brumptomyia França &amp; Parrot, 1921</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="D65">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3482,24 +3482,19 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Nyssomyia</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Nyssomyia neivai</t>
+          <t>Brumptomyia</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BRUMPTOMYIA SPP</t>
+          <t>MIGONEMYIA MIGONEI MIGONEI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Brumptomyia França &amp; Parrot, 1921</t>
+          <t>Migonemyia migonei França, 1920</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3508,7 +3503,7 @@
         </is>
       </c>
       <c r="D66">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3532,19 +3527,24 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Brumptomyia</t>
+          <t>Migonemyia</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Migonemyia migonei</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MIGONEMYIA MIGONEI MIGONEI</t>
+          <t>EVANDROMYIA LENTI LENTI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Migonemyia migonei França, 1920</t>
+          <t>Evandromyia lenti (Mangabeira, 1938)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3577,24 +3577,24 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Migonemyia</t>
+          <t>Evandromyia</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Migonemyia migonei</t>
+          <t>Evandromyia lenti</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EVANDROMYIA LENTI LENTI</t>
+          <t>LUTZOMYIA LONGIPALPIS LONGIPALPIS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Evandromyia lenti (Mangabeira, 1938)</t>
+          <t>Lutzomyia longipalpis (Lutz &amp; Neiva, 1912)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3627,24 +3627,24 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
+          <t>Lutzomyia</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Evandromyia lenti</t>
+          <t>Lutzomyia longipalpis</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LUTZOMYIA LONGIPALPIS LONGIPALPIS</t>
+          <t>NYSSOMYIA NEIVAI NEIVAI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lutzomyia longipalpis (Lutz &amp; Neiva, 1912)</t>
+          <t>Nyssomyia neivai (Pinto, 1926)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3677,24 +3677,24 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Lutzomyia</t>
+          <t>Nyssomyia</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Lutzomyia longipalpis</t>
+          <t>Nyssomyia neivai</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NYSSOMYIA NEIVAI NEIVAI</t>
+          <t>EVANDROMYIA CORTELEZZI CORTELEZZI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nyssomyia neivai (Pinto, 1926)</t>
+          <t>Evandromyia cortelezzii (Brèthes, 1923)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D70">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3727,24 +3727,24 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Nyssomyia</t>
+          <t>Evandromyia</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nyssomyia neivai</t>
+          <t>Evandromyia cortelezzii</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EVANDROMYIA CORTELEZZI CORTELEZZI</t>
+          <t>PSATHYROMYIA PUNTIGENICULATA PUNTIGENICULATA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Evandromyia cortelezzii (Brèthes, 1923)</t>
+          <t>Psathyromyia punctigeniculata (Floch &amp; Abonnenc, 1944)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="D71">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3777,24 +3777,24 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
+          <t>Psathyromyia</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Evandromyia cortelezzii</t>
+          <t>Psathyromyia punctigeniculata</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PSATHYROMYIA PUNTIGENICULATA PUNTIGENICULATA</t>
+          <t>BRUMPTOMYIA BRUMPTI BRUMPTI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Psathyromyia punctigeniculata (Floch &amp; Abonnenc, 1944)</t>
+          <t>Brumptomyia brumpti Larroussee</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="D72">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3827,24 +3827,24 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Psathyromyia</t>
+          <t>Brumptomyia</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Psathyromyia punctigeniculata</t>
+          <t>Brumptomyia brumpti</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BRUMPTOMYIA BRUMPTI BRUMPTI</t>
+          <t>EVANDROMYIA CORTELEZZII CORTELEZZII</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Brumptomyia brumpti Larroussee</t>
+          <t>Evandromyia cortelezzii (Brèthes, 1923)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3877,24 +3877,24 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Brumptomyia</t>
+          <t>Evandromyia</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Brumptomyia brumpti</t>
+          <t>Evandromyia cortelezzii</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EVANDROMYIA CORTELEZZII CORTELEZZII</t>
+          <t>BRUMPTOMYIA AVELLARI AVELLARI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Evandromyia cortelezzii (Brèthes, 1923)</t>
+          <t>Brumptomyia avellari (Lima, 1932)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3927,24 +3927,24 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Evandromyia</t>
+          <t>Brumptomyia</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Evandromyia cortelezzii</t>
+          <t>Brumptomyia avellari</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BRUMPTOMYIA AVELLARI AVELLARI</t>
+          <t>NYSSOMYIA WHITMANI WHITMANI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Brumptomyia avellari (Lima, 1932)</t>
+          <t>Nyssomyia whitmani (Antunes &amp; Coutinho, 1939)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3977,24 +3977,24 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Brumptomyia</t>
+          <t>Nyssomyia</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Brumptomyia avellari</t>
+          <t>Nyssomyia whitmani</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NYSSOMYIA WHITMANI WHITMANI</t>
+          <t>PINTOMYIA KUSCHELI KUSCHELI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nyssomyia whitmani (Antunes &amp; Coutinho, 1939)</t>
+          <t>Pintomyia kuscheli (Le Pont, Martínez &amp; Torrez-Espejo, 1998)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4027,24 +4027,24 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Nyssomyia</t>
+          <t>Pintomyia</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Nyssomyia whitmani</t>
+          <t>Pintomyia kuscheli</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PINTOMYIA KUSCHELI KUSCHELI</t>
+          <t>TRIATOMA SORDIDA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pintomyia kuscheli (Le Pont, Martínez &amp; Torrez-Espejo, 1998)</t>
+          <t>Triatoma sordida (Stål, 1859)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4067,34 +4067,34 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Diptera</t>
+          <t>Hemiptera</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Psychodidae</t>
+          <t>Reduviidae</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Pintomyia</t>
+          <t>Triatoma</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Pintomyia kuscheli</t>
+          <t>Triatoma sordida</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TRIATOMA SORDIDA</t>
+          <t>TRIATOMA GUASAYANA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Triatoma sordida (Stål, 1859)</t>
+          <t>Triatoma guasayana Wygodzinsky &amp; Abalos, 1949</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4132,19 +4132,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Triatoma sordida</t>
+          <t>Triatoma guasayana</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TRIATOMA GUASAYANA</t>
+          <t>TRIATOMA INFESTANS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Triatoma guasayana Wygodzinsky &amp; Abalos, 1949</t>
+          <t>Triatoma infestans (Klug, 1834)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4182,19 +4182,19 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Triatoma guasayana</t>
+          <t>Triatoma infestans</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TRIATOMA INFESTANS</t>
+          <t>PANSTRONGYLUS MEGISTUS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Triatoma infestans (Klug, 1834)</t>
+          <t>Panstrongylus megistus (Burmeister, 1835)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4227,24 +4227,24 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Triatoma</t>
+          <t>Panstrongylus</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Triatoma infestans</t>
+          <t>Panstrongylus megistus</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PANSTRONGYLUS MEGISTUS</t>
+          <t>PANSTRONGYLUS GENICULATUS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Panstrongylus megistus (Burmeister, 1835)</t>
+          <t>Panstrongylus geniculatus (Latreille, 1811)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4282,19 +4282,19 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Panstrongylus megistus</t>
+          <t>Panstrongylus geniculatus</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PANSTRONGYLUS GENICULATUS</t>
+          <t>TRIATOMA GUASU</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Panstrongylus geniculatus (Latreille, 1811)</t>
+          <t>Triatoma guazu Lent &amp; Wygodzinsky, 1979</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D82">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4327,24 +4327,24 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Panstrongylus</t>
+          <t>Triatoma</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Panstrongylus geniculatus</t>
+          <t>Triatoma guazu</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TRIATOMA GUASU</t>
+          <t>TRIATOMA PLATENSIS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Triatoma guazu Lent &amp; Wygodzinsky, 1979</t>
+          <t>Triatoma platensis Neiva, 1913</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="D83">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4382,79 +4382,74 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Triatoma guazu</t>
+          <t>Triatoma platensis</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TRIATOMA PLATENSIS</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Triatoma platensis Neiva, 1913</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
+          <t>HUEVOS</t>
         </is>
       </c>
       <c r="D84">
-        <v>99</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Animalia</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Arthropoda</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Hemiptera</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Reduviidae</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Triatoma</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Triatoma platensis</t>
-        </is>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HUEVOS</t>
+          <t>RHODNIUS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Rhodnius Stål, 1859</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="D85">
-        <v>100</v>
+        <v>94</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Animalia</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Arthropoda</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hemiptera</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Reduviidae</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Rhodnius</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RHODNIUS</t>
+          <t>TRIATOMA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rhodnius Stål, 1859</t>
+          <t>Triatoma Laporte, 1832</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4463,7 +4458,7 @@
         </is>
       </c>
       <c r="D86">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4487,19 +4482,19 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Rhodnius</t>
+          <t>Triatoma</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TRIATOMA</t>
+          <t>AEDES AEGYPTI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Triatoma Laporte, 1832</t>
+          <t>Aedes aegypti (Linnaeus, 1762)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4508,7 +4503,7 @@
         </is>
       </c>
       <c r="D87">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4522,29 +4517,34 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hemiptera</t>
+          <t>Diptera</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Reduviidae</t>
+          <t>Culicidae</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Triatoma</t>
+          <t>Aedes</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Aedes aegypti</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AEDES AEGYPTI</t>
+          <t>HAEMAGOGUS HAEMAGOGUS SPEGAZZINII</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Aedes aegypti (Linnaeus, 1762)</t>
+          <t>Haemagogus Williston, 1896</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="D88">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4577,24 +4577,19 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Aedes</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Aedes aegypti</t>
+          <t>Haemagogus</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HAEMAGOGUS HAEMAGOGUS SPEGAZZINII</t>
+          <t>PSOROPHORA JANTHINOSOMA FEROX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Haemagogus Williston, 1896</t>
+          <t>Psorophora Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4627,19 +4622,19 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Haemagogus</t>
+          <t>Psorophora</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PSOROPHORA JANTHINOSOMA FEROX</t>
+          <t>OCHLEROTATUS CHRYSOCONOPS FULVUS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Psorophora Robineau-Desvoidy, 1827</t>
+          <t>Ochlerotatus Lynch-Arribalzaga, 1891</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4648,7 +4643,7 @@
         </is>
       </c>
       <c r="D90">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4672,14 +4667,14 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Psorophora</t>
+          <t>Ochlerotatus</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OCHLEROTATUS CHRYSOCONOPS FULVUS</t>
+          <t>OCHLEROTATUS OCHLEROTATUS SCAPULARIS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4724,21 +4719,21 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OCHLEROTATUS OCHLEROTATUS SCAPULARIS</t>
+          <t>OCHLEROTATUS SERRATUS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ochlerotatus Lynch-Arribalzaga, 1891</t>
+          <t>Ochlerotatus serratus (Theobald, 1901)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>SYNONYM</t>
         </is>
       </c>
       <c r="D92">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4762,28 +4757,33 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Ochlerotatus</t>
+          <t>Aedes</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Aedes serratus</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OCHLEROTATUS SERRATUS</t>
+          <t>PSOROPHORA JANTHINOSOMA ALBIGENU</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ochlerotatus serratus (Theobald, 1901)</t>
+          <t>Psorophora Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SYNONYM</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="D93">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4807,24 +4807,19 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Aedes</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Aedes serratus</t>
+          <t>Psorophora</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PSOROPHORA JANTHINOSOMA ALBIGENU</t>
+          <t>HAEMAGOGUS HAEMAGOGUS CELESTE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Psorophora Robineau-Desvoidy, 1827</t>
+          <t>Haemagogus Williston, 1896</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4857,19 +4852,19 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Psorophora</t>
+          <t>Haemagogus</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>HAEMAGOGUS HAEMAGOGUS CELESTE</t>
+          <t>SABETHES SABETHINUS INTERMEDIUS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Haemagogus Williston, 1896</t>
+          <t>Sabethes Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4902,19 +4897,19 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Haemagogus</t>
+          <t>Sabethes</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SABETHES SABETHINUS INTERMEDIUS</t>
+          <t>AEDES STEGOMYIA AEGYPTI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sabethes Robineau-Desvoidy, 1827</t>
+          <t>Aedes Meigen, 1818</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4947,19 +4942,19 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Sabethes</t>
+          <t>Aedes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AEDES STEGOMYIA AEGYPTI</t>
+          <t>SABETHES SABETHES QUASICYANEUS</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Aedes Meigen, 1818</t>
+          <t>Sabethes Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4992,14 +4987,14 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Aedes</t>
+          <t>Sabethes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SABETHES SABETHES QUASICYANEUS</t>
+          <t>SABETHES SABETHOIDES CHLOROPTERUS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5044,7 +5039,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SABETHES SABETHOIDES CHLOROPTERUS</t>
+          <t>SABETHES SABETHOIDES GLAUCODAEMON</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5089,12 +5084,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SABETHES SABETHOIDES GLAUCODAEMON</t>
+          <t>PSOROPHORA JANTHINOSOMA LUTZII</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Sabethes Robineau-Desvoidy, 1827</t>
+          <t>Psorophora Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5127,19 +5122,19 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Sabethes</t>
+          <t>Psorophora</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PSOROPHORA JANTHINOSOMA LUTZII</t>
+          <t>SABETHES SABETHES BELISARIOI</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Psorophora Robineau-Desvoidy, 1827</t>
+          <t>Sabethes Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5172,19 +5167,19 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Psorophora</t>
+          <t>Sabethes</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SABETHES SABETHES BELISARIOI</t>
+          <t>WYEOMYIA TRIAMYIA APORONOMA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sabethes Robineau-Desvoidy, 1827</t>
+          <t>Wyeomyia Theobald, 1901</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5217,19 +5212,19 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Sabethes</t>
+          <t>Wyeomyia</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>WYEOMYIA TRIAMYIA APORONOMA</t>
+          <t>SABETHES SABETHES ALBIPRIVUS</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wyeomyia Theobald, 1901</t>
+          <t>Sabethes Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5262,14 +5257,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Wyeomyia</t>
+          <t>Sabethes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SABETHES SABETHES ALBIPRIVUS</t>
+          <t>SABETHES SABETHES BIPARTIPES</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5314,12 +5309,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SABETHES SABETHES BIPARTIPES</t>
+          <t>HAEMAGOGUS CONOPOSTEGUS LEUCOCELAENUS</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sabethes Robineau-Desvoidy, 1827</t>
+          <t>Haemagogus Williston, 1896</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5352,19 +5347,19 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Sabethes</t>
+          <t>Haemagogus</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HAEMAGOGUS CONOPOSTEGUS LEUCOCELAENUS</t>
+          <t>OCHLEROTATUS FLUVIATILIS</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Haemagogus Williston, 1896</t>
+          <t>Ochlerotatus Lynch-Arribalzaga, 1891</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5373,7 +5368,7 @@
         </is>
       </c>
       <c r="D106">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5397,19 +5392,19 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Haemagogus</t>
+          <t>Ochlerotatus</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OCHLEROTATUS FLUVIATILIS</t>
+          <t>SABETHES BELISARIOI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ochlerotatus Lynch-Arribalzaga, 1891</t>
+          <t>Sabethes belisarioi Neiva, 1908</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5418,7 +5413,7 @@
         </is>
       </c>
       <c r="D107">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5442,19 +5437,24 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Ochlerotatus</t>
+          <t>Sabethes</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Sabethes belisarioi</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SABETHES BELISARIOI</t>
+          <t>SABETHES SABETHES AMAZONICUS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sabethes belisarioi Neiva, 1908</t>
+          <t>Sabethes Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="D108">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5488,18 +5488,13 @@
       <c r="I108" t="inlineStr">
         <is>
           <t>Sabethes</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Sabethes belisarioi</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SABETHES SABETHES AMAZONICUS</t>
+          <t>SABETHES SABETHES PURPUREUS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5544,12 +5539,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SABETHES SABETHES PURPUREUS</t>
+          <t>PSOROPHORA ALBIGENU</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sabethes Robineau-Desvoidy, 1827</t>
+          <t>Psorophora albigenu Peryassú</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -5558,7 +5553,7 @@
         </is>
       </c>
       <c r="D110">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5582,28 +5577,33 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Sabethes</t>
+          <t>Psorophora</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Psorophora albigenu</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PSOROPHORA ALBIGENU</t>
+          <t>OCHLEROTATUS HASTATUS</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Psorophora albigenu Peryassú</t>
+          <t>Ochlerotatus hastatus (Dyar, 1922)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ACCEPTED</t>
+          <t>SYNONYM</t>
         </is>
       </c>
       <c r="D111">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5627,33 +5627,33 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Psorophora</t>
+          <t>Aedes</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Psorophora albigenu</t>
+          <t>Aedes hastatus</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OCHLEROTATUS HASTATUS</t>
+          <t>PSOROPHORA JANTHINOSOMA ALBIPES</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ochlerotatus hastatus (Dyar, 1922)</t>
+          <t>Psorophora Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SYNONYM</t>
+          <t>ACCEPTED</t>
         </is>
       </c>
       <c r="D112">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5677,24 +5677,19 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Aedes</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Aedes hastatus</t>
+          <t>Psorophora</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PSOROPHORA JANTHINOSOMA ALBIPES</t>
+          <t>PSOROPHORA FEROX</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Psorophora Robineau-Desvoidy, 1827</t>
+          <t>Psorophora ferox (Humboldt, 1819)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -5703,7 +5698,7 @@
         </is>
       </c>
       <c r="D113">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5728,18 +5723,23 @@
       <c r="I113" t="inlineStr">
         <is>
           <t>Psorophora</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Psorophora ferox</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PSOROPHORA FEROX</t>
+          <t>LIMATUS DURHAMII</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Psorophora ferox (Humboldt, 1819)</t>
+          <t>Limatus durhamii Theobald, 1901</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5772,24 +5772,24 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Psorophora</t>
+          <t>Limatus</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Psorophora ferox</t>
+          <t>Limatus durhamii</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LIMATUS DURHAMII</t>
+          <t>PSOROPHORA PSOROPHORA CILIATA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Limatus durhamii Theobald, 1901</t>
+          <t>Psorophora Robineau-Desvoidy, 1827</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="D115">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -5821,56 +5821,6 @@
         </is>
       </c>
       <c r="I115" t="inlineStr">
-        <is>
-          <t>Limatus</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Limatus durhamii</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>PSOROPHORA PSOROPHORA CILIATA</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Psorophora Robineau-Desvoidy, 1827</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>ACCEPTED</t>
-        </is>
-      </c>
-      <c r="D116">
-        <v>94</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Animalia</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Arthropoda</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Diptera</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Culicidae</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
         <is>
           <t>Psorophora</t>
         </is>
